--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,23 +454,28 @@
           <t>Unit 7</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
       <c r="C2" t="n">
-        <v>17.88425</v>
+        <v>17.95804</v>
       </c>
       <c r="D2" t="n">
-        <v>18.01896</v>
+        <v>17.30153</v>
       </c>
       <c r="E2" t="n">
-        <v>17.83892</v>
+        <v>17.5962</v>
       </c>
       <c r="F2" t="n">
-        <v>44.59914</v>
+        <v>43.96227</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05318</v>
+        <v>0.05446</v>
       </c>
       <c r="H2" t="n">
-        <v>1.87963</v>
+        <v>1.99276</v>
       </c>
     </row>
     <row r="3">
@@ -480,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.0675</v>
+        <v>17.62316</v>
       </c>
       <c r="D3" t="n">
-        <v>17.57121</v>
+        <v>17.07954</v>
       </c>
       <c r="E3" t="n">
-        <v>17.6527</v>
+        <v>17.50568</v>
       </c>
       <c r="F3" t="n">
-        <v>44.65397</v>
+        <v>45.34342</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05316</v>
+        <v>0.05367</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9281</v>
+        <v>1.90637</v>
       </c>
     </row>
     <row r="4">
@@ -505,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.82988</v>
+        <v>17.80992</v>
       </c>
       <c r="D4" t="n">
-        <v>17.85694</v>
+        <v>17.40148</v>
       </c>
       <c r="E4" t="n">
-        <v>17.88504</v>
+        <v>17.7973</v>
       </c>
       <c r="F4" t="n">
-        <v>44.82911</v>
+        <v>45.69751</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05446</v>
+        <v>0.05444</v>
       </c>
       <c r="H4" t="n">
-        <v>1.93613</v>
+        <v>1.94893</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.47101</v>
+        <v>17.78229</v>
       </c>
       <c r="D5" t="n">
-        <v>17.94638</v>
+        <v>17.53133</v>
       </c>
       <c r="E5" t="n">
-        <v>17.67858</v>
+        <v>17.54402</v>
       </c>
       <c r="F5" t="n">
-        <v>44.56257</v>
+        <v>45.4256</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05399</v>
+        <v>0.0535</v>
       </c>
       <c r="H5" t="n">
-        <v>1.90887</v>
+        <v>1.9045</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.88123</v>
+        <v>17.39513</v>
       </c>
       <c r="D6" t="n">
-        <v>17.40335</v>
+        <v>17.08393</v>
       </c>
       <c r="E6" t="n">
-        <v>17.4855</v>
+        <v>17.33632</v>
       </c>
       <c r="F6" t="n">
-        <v>45.11802</v>
+        <v>44.41267</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05307</v>
+        <v>0.05287</v>
       </c>
       <c r="H6" t="n">
-        <v>1.91164</v>
+        <v>1.9074</v>
       </c>
     </row>
     <row r="7">
@@ -580,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18.00998</v>
+        <v>18.09616</v>
       </c>
       <c r="D7" t="n">
-        <v>17.52503</v>
+        <v>17.72735</v>
       </c>
       <c r="E7" t="n">
-        <v>17.8065</v>
+        <v>17.86915</v>
       </c>
       <c r="F7" t="n">
-        <v>45.14936</v>
+        <v>44.1447</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05508</v>
+        <v>0.05467</v>
       </c>
       <c r="H7" t="n">
-        <v>1.91097</v>
+        <v>1.92551</v>
       </c>
     </row>
     <row r="8">
@@ -605,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.87601</v>
+        <v>17.636</v>
       </c>
       <c r="D8" t="n">
-        <v>17.63855</v>
+        <v>17.40192</v>
       </c>
       <c r="E8" t="n">
-        <v>18.14375</v>
+        <v>17.57969</v>
       </c>
       <c r="F8" t="n">
-        <v>44.93602</v>
+        <v>45.7207</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05457</v>
+        <v>0.05334</v>
       </c>
       <c r="H8" t="n">
-        <v>1.94157</v>
+        <v>1.92821</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.493</v>
+        <v>18.36395</v>
       </c>
       <c r="D9" t="n">
-        <v>17.27001</v>
+        <v>17.84535</v>
       </c>
       <c r="E9" t="n">
-        <v>17.48264</v>
+        <v>17.95061</v>
       </c>
       <c r="F9" t="n">
-        <v>44.8998</v>
+        <v>44.43773</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05399</v>
+        <v>0.05411</v>
       </c>
       <c r="H9" t="n">
-        <v>1.92443</v>
+        <v>1.87536</v>
       </c>
     </row>
     <row r="10">
@@ -655,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.73584</v>
+        <v>18.02529</v>
       </c>
       <c r="D10" t="n">
-        <v>17.90226</v>
+        <v>17.54646</v>
       </c>
       <c r="E10" t="n">
-        <v>17.56411</v>
+        <v>17.63938</v>
       </c>
       <c r="F10" t="n">
-        <v>44.5045</v>
+        <v>45.17417</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05381</v>
+        <v>0.05416</v>
       </c>
       <c r="H10" t="n">
-        <v>1.94718</v>
+        <v>1.91692</v>
       </c>
     </row>
     <row r="11">
@@ -713,26 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.3572</v>
+        <v>17.86177</v>
       </c>
       <c r="D12" t="n">
-        <v>17.67999</v>
+        <v>17.74801</v>
       </c>
       <c r="E12" t="n">
-        <v>17.0568</v>
+        <v>17.79572</v>
       </c>
       <c r="F12" t="n">
-        <v>44.53681</v>
+        <v>45.66058</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05314</v>
+        <v>0.05405</v>
       </c>
       <c r="H12" t="n">
-        <v>1.91025</v>
+        <v>1.95712</v>
       </c>
     </row>
     <row r="13">
@@ -742,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.58906</v>
+        <v>17.85698</v>
       </c>
       <c r="D13" t="n">
-        <v>17.48678</v>
+        <v>17.54077</v>
       </c>
       <c r="E13" t="n">
-        <v>17.50788</v>
+        <v>17.64227</v>
       </c>
       <c r="F13" t="n">
-        <v>44.07379</v>
+        <v>46.28385</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05426</v>
+        <v>0.05342</v>
       </c>
       <c r="H13" t="n">
-        <v>1.88945</v>
+        <v>1.92662</v>
       </c>
     </row>
     <row r="14">
@@ -767,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.40521</v>
+        <v>17.73798</v>
       </c>
       <c r="D14" t="n">
-        <v>17.81576</v>
+        <v>17.36168</v>
       </c>
       <c r="E14" t="n">
-        <v>17.9545</v>
+        <v>17.54537</v>
       </c>
       <c r="F14" t="n">
-        <v>44.88207</v>
+        <v>45.38446</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05463</v>
+        <v>0.05304</v>
       </c>
       <c r="H14" t="n">
-        <v>1.93257</v>
+        <v>1.93823</v>
       </c>
     </row>
     <row r="15">
@@ -792,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.79518</v>
+        <v>18.18207</v>
       </c>
       <c r="D15" t="n">
-        <v>17.45471</v>
+        <v>17.79772</v>
       </c>
       <c r="E15" t="n">
-        <v>17.58902</v>
+        <v>17.81623</v>
       </c>
       <c r="F15" t="n">
-        <v>45.521</v>
+        <v>46.49422</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05443</v>
+        <v>0.05444</v>
       </c>
       <c r="H15" t="n">
-        <v>1.94067</v>
+        <v>1.91354</v>
       </c>
     </row>
     <row r="16">
@@ -817,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.95881</v>
+        <v>17.97846</v>
       </c>
       <c r="D16" t="n">
-        <v>17.32265</v>
+        <v>17.50983</v>
       </c>
       <c r="E16" t="n">
-        <v>17.44025</v>
+        <v>17.91594</v>
       </c>
       <c r="F16" t="n">
-        <v>45.77692</v>
+        <v>44.39298</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05361</v>
+        <v>0.05396</v>
       </c>
       <c r="H16" t="n">
-        <v>1.87896</v>
+        <v>1.91712</v>
       </c>
     </row>
     <row r="17">
@@ -842,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.66809</v>
+        <v>18.27326</v>
       </c>
       <c r="D17" t="n">
-        <v>17.73337</v>
+        <v>17.66223</v>
       </c>
       <c r="E17" t="n">
-        <v>17.84145</v>
+        <v>17.7296</v>
       </c>
       <c r="F17" t="n">
-        <v>45.7024</v>
+        <v>45.50306</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05443</v>
+        <v>0.05336</v>
       </c>
       <c r="H17" t="n">
-        <v>1.91939</v>
+        <v>1.96857</v>
       </c>
     </row>
     <row r="18">
@@ -867,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.64438</v>
+        <v>18.05256</v>
       </c>
       <c r="D18" t="n">
-        <v>17.99976</v>
+        <v>17.20107</v>
       </c>
       <c r="E18" t="n">
-        <v>17.6669</v>
+        <v>17.86369</v>
       </c>
       <c r="F18" t="n">
-        <v>45.02587</v>
+        <v>45.82654</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05355</v>
+        <v>0.05359</v>
       </c>
       <c r="H18" t="n">
-        <v>1.93578</v>
+        <v>1.93246</v>
       </c>
     </row>
     <row r="19">
@@ -892,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18.06115</v>
+        <v>18.11666</v>
       </c>
       <c r="D19" t="n">
-        <v>17.66867</v>
+        <v>17.51836</v>
       </c>
       <c r="E19" t="n">
-        <v>17.63616</v>
+        <v>17.53755</v>
       </c>
       <c r="F19" t="n">
-        <v>45.15481</v>
+        <v>44.86254</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05398</v>
+        <v>0.05377</v>
       </c>
       <c r="H19" t="n">
-        <v>1.95107</v>
+        <v>1.94355</v>
       </c>
     </row>
     <row r="20">
@@ -917,63 +922,43 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.6921</v>
+        <v>17.69788</v>
       </c>
       <c r="D20" t="n">
-        <v>17.3897</v>
+        <v>17.50262</v>
       </c>
       <c r="E20" t="n">
-        <v>17.65812</v>
+        <v>17.5329</v>
       </c>
       <c r="F20" t="n">
-        <v>45.28664</v>
+        <v>44.78641</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05304</v>
+        <v>0.05327</v>
       </c>
       <c r="H20" t="n">
-        <v>1.92033</v>
+        <v>1.91551</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -985,32 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.79959</v>
+        <v>16.52772</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08774</v>
+        <v>16.43026</v>
       </c>
       <c r="E22" t="n">
-        <v>0.63978</v>
+        <v>16.48424</v>
       </c>
       <c r="F22" t="n">
-        <v>1.02349</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.11719</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00793</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09939000000000001</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.13266</v>
+        <v>272.8021</v>
       </c>
     </row>
     <row r="23">
@@ -1020,28 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.78333</v>
+        <v>16.95013</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0858</v>
+        <v>16.54634</v>
       </c>
       <c r="E23" t="n">
-        <v>0.63573</v>
+        <v>16.66658</v>
       </c>
       <c r="F23" t="n">
-        <v>1.03101</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.11681</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00804</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09841</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.13317</v>
+        <v>270.64072</v>
       </c>
     </row>
     <row r="24">
@@ -1051,28 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.7988</v>
+        <v>16.71451</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08656999999999999</v>
+        <v>16.42701</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6441</v>
+        <v>16.61716</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0276</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.11447</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.008030000000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09882000000000001</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.13565</v>
+        <v>266.82343</v>
       </c>
     </row>
     <row r="25">
@@ -1082,28 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.78046</v>
+        <v>16.66641</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08678</v>
+        <v>16.20436</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6325499999999999</v>
+        <v>16.27791</v>
       </c>
       <c r="F25" t="n">
-        <v>1.01945</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.11698</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00804</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09811</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.13263</v>
+        <v>267.83158</v>
       </c>
     </row>
     <row r="26">
@@ -1113,28 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.80124</v>
+        <v>16.59817</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08595999999999999</v>
+        <v>16.19338</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6494</v>
+        <v>16.53314</v>
       </c>
       <c r="F26" t="n">
-        <v>1.01912</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.11399</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00808</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09708</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.13375</v>
+        <v>263.5073</v>
       </c>
     </row>
     <row r="27">
@@ -1144,28 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.80036</v>
+        <v>16.58962</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08451</v>
+        <v>16.44452</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6346000000000001</v>
+        <v>16.45997</v>
       </c>
       <c r="F27" t="n">
-        <v>1.02461</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.1169</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.008109999999999999</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09643</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.13413</v>
+        <v>270.70775</v>
       </c>
     </row>
     <row r="28">
@@ -1175,28 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.80106</v>
+        <v>16.7774</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08619</v>
+        <v>16.44909</v>
       </c>
       <c r="E28" t="n">
-        <v>0.63474</v>
+        <v>16.64308</v>
       </c>
       <c r="F28" t="n">
-        <v>1.04134</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.1166</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00808</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09859</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.13436</v>
+        <v>268.87788</v>
       </c>
     </row>
     <row r="29">
@@ -1206,28 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.78631</v>
+        <v>16.60888</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08404</v>
+        <v>16.18577</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6463</v>
+        <v>16.45396</v>
       </c>
       <c r="F29" t="n">
-        <v>1.01718</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.11537</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00812</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09897</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.13186</v>
+        <v>267.83496</v>
       </c>
     </row>
     <row r="30">
@@ -1237,28 +1126,1070 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.8178299999999999</v>
+        <v>16.62763</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08792999999999999</v>
+        <v>16.38688</v>
       </c>
       <c r="E30" t="n">
-        <v>0.64431</v>
+        <v>16.46625</v>
       </c>
       <c r="F30" t="n">
+        <v>270.43651</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>17.50067</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.91465</v>
+      </c>
+      <c r="E32" t="n">
+        <v>17.38843</v>
+      </c>
+      <c r="F32" t="n">
+        <v>23.07818</v>
+      </c>
+      <c r="G32" t="n">
+        <v>36.41343</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.71602</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.89226</v>
+      </c>
+      <c r="E33" t="n">
+        <v>17.47723</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22.76351</v>
+      </c>
+      <c r="G33" t="n">
+        <v>35.97391</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17.82155</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.94621</v>
+      </c>
+      <c r="E34" t="n">
+        <v>17.37262</v>
+      </c>
+      <c r="F34" t="n">
+        <v>22.7294</v>
+      </c>
+      <c r="G34" t="n">
+        <v>36.41175</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.75331</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.99672</v>
+      </c>
+      <c r="E35" t="n">
+        <v>17.31455</v>
+      </c>
+      <c r="F35" t="n">
+        <v>23.11485</v>
+      </c>
+      <c r="G35" t="n">
+        <v>36.58398</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17.55072</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.91051</v>
+      </c>
+      <c r="E36" t="n">
+        <v>17.3612</v>
+      </c>
+      <c r="F36" t="n">
+        <v>23.31974</v>
+      </c>
+      <c r="G36" t="n">
+        <v>36.4726</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>18.00408</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.98156</v>
+      </c>
+      <c r="E37" t="n">
+        <v>17.67054</v>
+      </c>
+      <c r="F37" t="n">
+        <v>22.49061</v>
+      </c>
+      <c r="G37" t="n">
+        <v>36.26382</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>17.47797</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.70191</v>
+      </c>
+      <c r="E38" t="n">
+        <v>17.35896</v>
+      </c>
+      <c r="F38" t="n">
+        <v>23.11396</v>
+      </c>
+      <c r="G38" t="n">
+        <v>35.70037</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>17.97716</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.86515</v>
+      </c>
+      <c r="E39" t="n">
+        <v>17.15147</v>
+      </c>
+      <c r="F39" t="n">
+        <v>23.10318</v>
+      </c>
+      <c r="G39" t="n">
+        <v>35.87361</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>17.869</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.6866</v>
+      </c>
+      <c r="E40" t="n">
+        <v>17.49013</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22.97702</v>
+      </c>
+      <c r="G40" t="n">
+        <v>35.80148</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>17.39729</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.88601</v>
+      </c>
+      <c r="E42" t="n">
+        <v>17.39476</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.8245</v>
+      </c>
+      <c r="G42" t="n">
+        <v>36.0513</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>17.97964</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.70696</v>
+      </c>
+      <c r="E43" t="n">
+        <v>17.24675</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.92718</v>
+      </c>
+      <c r="G43" t="n">
+        <v>36.42155</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>17.78016</v>
+      </c>
+      <c r="D44" t="n">
+        <v>17.03516</v>
+      </c>
+      <c r="E44" t="n">
+        <v>17.44402</v>
+      </c>
+      <c r="F44" t="n">
+        <v>23.20589</v>
+      </c>
+      <c r="G44" t="n">
+        <v>36.63292</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>17.5011</v>
+      </c>
+      <c r="D45" t="n">
+        <v>17.03958</v>
+      </c>
+      <c r="E45" t="n">
+        <v>17.49161</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22.97874</v>
+      </c>
+      <c r="G45" t="n">
+        <v>35.95001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>17.82742</v>
+      </c>
+      <c r="D46" t="n">
+        <v>17.42376</v>
+      </c>
+      <c r="E46" t="n">
+        <v>17.78007</v>
+      </c>
+      <c r="F46" t="n">
+        <v>23.0848</v>
+      </c>
+      <c r="G46" t="n">
+        <v>35.81129</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>17.48938</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.9606</v>
+      </c>
+      <c r="E47" t="n">
+        <v>17.01699</v>
+      </c>
+      <c r="F47" t="n">
+        <v>23.04946</v>
+      </c>
+      <c r="G47" t="n">
+        <v>36.69078</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>17.49061</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.79505</v>
+      </c>
+      <c r="E48" t="n">
+        <v>17.33162</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.37576</v>
+      </c>
+      <c r="G48" t="n">
+        <v>36.53839</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>17.70791</v>
+      </c>
+      <c r="D49" t="n">
+        <v>17.03469</v>
+      </c>
+      <c r="E49" t="n">
+        <v>17.37949</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22.89231</v>
+      </c>
+      <c r="G49" t="n">
+        <v>36.8048</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>18.07229</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.71138</v>
+      </c>
+      <c r="E50" t="n">
+        <v>17.583</v>
+      </c>
+      <c r="F50" t="n">
+        <v>23.20987</v>
+      </c>
+      <c r="G50" t="n">
+        <v>36.34887</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.64008</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.20004</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.65093</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.1542</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.6396500000000001</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.18398</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.63869</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.19123</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.65703</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.14351</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6391</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.18459</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.6182</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.19225</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.63539</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.18819</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.65866</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.18444</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.64551</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.17857</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.64446</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.15888</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.64102</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.17444</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.6505300000000001</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.16887</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.6493100000000001</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.15581</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.64576</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.16948</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.17238</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.64272</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.18855</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.63841</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.16488</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.7960700000000001</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.08619</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.6452</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.02191</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.11467</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.00818</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09923999999999999</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.13613</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.77535</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.08527</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.62973</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.03252</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.11353</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00808</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09923999999999999</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.13238</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.79453</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.08494</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.6505</v>
+      </c>
+      <c r="F74" t="n">
         <v>0.9958900000000001</v>
       </c>
-      <c r="G30" t="n">
-        <v>0.1169</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00805</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09913</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.13443</v>
+      <c r="G74" t="n">
+        <v>0.11652</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.007979999999999999</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.10003</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.13578</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.79454</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08506</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.6394</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.00451</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.11557</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09746</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.13681</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.79403</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08697000000000001</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.64855</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.01978</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.11551</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.008019999999999999</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.10033</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.1326</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.78835</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08445</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.6482</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.02721</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.11353</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00809</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09838</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.13333</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.79023</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08482000000000001</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.65234</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.99122</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.11545</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00793</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09968</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.13132</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.78469</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08588</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.63792</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.0147</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.11623</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09927</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.13353</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.08624999999999999</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.6414</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.00889</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.11619</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.007979999999999999</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09822</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.1361</v>
       </c>
     </row>
   </sheetData>
